--- a/project/outputs_xlsx_solution/test33.4-wide-NC-1.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NC-1.xlsx
@@ -927,9 +927,6 @@
       <c r="DO1">
         <v>116</v>
       </c>
-      <c r="DP1">
-        <v>117</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1273,7 +1270,7 @@
         <v>15</v>
       </c>
       <c r="S13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T13" t="s">
         <v>14</v>
@@ -1285,9 +1282,6 @@
         <v>14</v>
       </c>
       <c r="W13" t="s">
-        <v>14</v>
-      </c>
-      <c r="X13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1322,7 +1316,7 @@
       <c r="O14" t="s">
         <v>21</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="X14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1363,7 +1357,7 @@
       <c r="R15" t="s">
         <v>21</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="Y15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1384,7 +1378,7 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="M16" t="s">
         <v>14</v>
@@ -1392,7 +1386,7 @@
       <c r="N16" t="s">
         <v>21</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="Z16" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1424,7 +1418,7 @@
       <c r="O17" t="s">
         <v>21</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AA17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1453,7 +1447,7 @@
       <c r="N18" t="s">
         <v>21</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AB18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1482,7 +1476,7 @@
       <c r="O19" t="s">
         <v>21</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AC19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1509,7 +1503,7 @@
         <v>16</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="P20" t="s">
         <v>14</v>
@@ -1521,12 +1515,9 @@
         <v>14</v>
       </c>
       <c r="S20" t="s">
-        <v>14</v>
-      </c>
-      <c r="T20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1549,6 +1540,9 @@
       <c r="O21" t="s">
         <v>33</v>
       </c>
+      <c r="S21" t="s">
+        <v>14</v>
+      </c>
       <c r="T21" t="s">
         <v>14</v>
       </c>
@@ -1556,12 +1550,9 @@
         <v>14</v>
       </c>
       <c r="V21" t="s">
-        <v>14</v>
-      </c>
-      <c r="W21" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1584,13 +1575,13 @@
       <c r="O22" t="s">
         <v>33</v>
       </c>
+      <c r="V22" t="s">
+        <v>14</v>
+      </c>
       <c r="W22" t="s">
-        <v>14</v>
-      </c>
-      <c r="X22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG22" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF22" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1611,15 +1602,12 @@
         <v>9</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="P23" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG23" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1640,15 +1628,12 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="Q24" t="s">
-        <v>14</v>
-      </c>
-      <c r="R24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH24" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1662,22 +1647,19 @@
       <c r="C25" t="s">
         <v>27</v>
       </c>
+      <c r="Q25" t="s">
+        <v>5</v>
+      </c>
       <c r="R25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S25" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T25" t="s">
-        <v>33</v>
-      </c>
-      <c r="U25" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ25" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1691,20 +1673,26 @@
       <c r="C26" t="s">
         <v>28</v>
       </c>
+      <c r="Q26" t="s">
+        <v>5</v>
+      </c>
       <c r="R26" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S26" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="T26" t="s">
-        <v>33</v>
+        <v>15</v>
+      </c>
+      <c r="U26" t="s">
+        <v>15</v>
       </c>
       <c r="V26" t="s">
         <v>15</v>
       </c>
       <c r="W26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X26" t="s">
         <v>14</v>
@@ -1716,12 +1704,9 @@
         <v>14</v>
       </c>
       <c r="AA26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ26" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1735,15 +1720,18 @@
       <c r="C27" t="s">
         <v>29</v>
       </c>
+      <c r="Q27" t="s">
+        <v>5</v>
+      </c>
       <c r="R27" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S27" t="s">
-        <v>9</v>
-      </c>
-      <c r="T27" t="s">
         <v>33</v>
       </c>
+      <c r="AA27" t="s">
+        <v>14</v>
+      </c>
       <c r="AB27" t="s">
         <v>14</v>
       </c>
@@ -1751,12 +1739,9 @@
         <v>14</v>
       </c>
       <c r="AD27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL27" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK27" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1770,22 +1755,22 @@
       <c r="C28" t="s">
         <v>30</v>
       </c>
+      <c r="Q28" t="s">
+        <v>5</v>
+      </c>
       <c r="R28" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S28" t="s">
-        <v>9</v>
-      </c>
-      <c r="T28" t="s">
         <v>33</v>
       </c>
+      <c r="AD28" t="s">
+        <v>14</v>
+      </c>
       <c r="AE28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM28" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1799,11 +1784,14 @@
       <c r="C29" t="s">
         <v>31</v>
       </c>
+      <c r="R29" t="s">
+        <v>5</v>
+      </c>
       <c r="S29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T29" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="U29" t="s">
         <v>34</v>
@@ -1812,18 +1800,12 @@
         <v>34</v>
       </c>
       <c r="W29" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="X29" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM29" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1837,25 +1819,22 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
+      <c r="R30" t="s">
+        <v>5</v>
+      </c>
       <c r="S30" t="s">
-        <v>5</v>
-      </c>
-      <c r="T30" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="W30" t="s">
+        <v>34</v>
       </c>
       <c r="X30" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1869,25 +1848,22 @@
       <c r="C31" t="s">
         <v>27</v>
       </c>
+      <c r="S31" t="s">
+        <v>5</v>
+      </c>
       <c r="T31" t="s">
-        <v>5</v>
-      </c>
-      <c r="U31" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="X31" t="s">
+        <v>34</v>
       </c>
       <c r="Y31" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="Z31" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>21</v>
-      </c>
-      <c r="AP31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1901,17 +1877,20 @@
       <c r="C32" t="s">
         <v>28</v>
       </c>
+      <c r="S32" t="s">
+        <v>5</v>
+      </c>
       <c r="T32" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>34</v>
       </c>
       <c r="Z32" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="AB32" t="s">
         <v>14</v>
@@ -1923,12 +1902,9 @@
         <v>14</v>
       </c>
       <c r="AE32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ32" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP32" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1942,18 +1918,21 @@
       <c r="C33" t="s">
         <v>29</v>
       </c>
+      <c r="S33" t="s">
+        <v>5</v>
+      </c>
       <c r="T33" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>34</v>
       </c>
       <c r="AA33" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB33" t="s">
         <v>33</v>
       </c>
+      <c r="AE33" t="s">
+        <v>14</v>
+      </c>
       <c r="AF33" t="s">
         <v>14</v>
       </c>
@@ -1961,12 +1940,9 @@
         <v>14</v>
       </c>
       <c r="AH33" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI33" t="s">
-        <v>21</v>
-      </c>
-      <c r="AR33" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ33" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1980,25 +1956,25 @@
       <c r="C34" t="s">
         <v>30</v>
       </c>
+      <c r="S34" t="s">
+        <v>5</v>
+      </c>
       <c r="T34" t="s">
-        <v>5</v>
-      </c>
-      <c r="U34" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>34</v>
       </c>
       <c r="AB34" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC34" t="s">
         <v>33</v>
       </c>
+      <c r="AH34" t="s">
+        <v>14</v>
+      </c>
       <c r="AI34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>21</v>
-      </c>
-      <c r="AS34" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR34" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2012,25 +1988,22 @@
       <c r="C35" t="s">
         <v>31</v>
       </c>
+      <c r="T35" t="s">
+        <v>5</v>
+      </c>
       <c r="U35" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>34</v>
       </c>
       <c r="AC35" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AD35" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>21</v>
-      </c>
-      <c r="AT35" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS35" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2044,25 +2017,22 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
+      <c r="T36" t="s">
+        <v>5</v>
+      </c>
       <c r="U36" t="s">
-        <v>5</v>
-      </c>
-      <c r="V36" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>34</v>
       </c>
       <c r="AD36" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AE36" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>21</v>
-      </c>
-      <c r="AU36" t="s">
+        <v>21</v>
+      </c>
+      <c r="AT36" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2076,25 +2046,25 @@
       <c r="C37" t="s">
         <v>35</v>
       </c>
+      <c r="AE37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>9</v>
+      </c>
       <c r="AG37" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AH37" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AI37" t="s">
         <v>14</v>
       </c>
       <c r="AJ37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL37" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV37" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU37" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2108,28 +2078,28 @@
       <c r="C38" t="s">
         <v>36</v>
       </c>
+      <c r="AE38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>9</v>
+      </c>
       <c r="AG38" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI38" t="s">
         <v>33</v>
       </c>
+      <c r="AJ38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>14</v>
+      </c>
       <c r="AL38" t="s">
         <v>14</v>
       </c>
       <c r="AM38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW38" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV38" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2143,19 +2113,19 @@
       <c r="C39" t="s">
         <v>37</v>
       </c>
+      <c r="AE39" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>9</v>
+      </c>
       <c r="AG39" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AH39" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>21</v>
-      </c>
-      <c r="AX39" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW39" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2169,16 +2139,19 @@
       <c r="C40" t="s">
         <v>38</v>
       </c>
+      <c r="AE40" t="s">
+        <v>5</v>
+      </c>
       <c r="AG40" t="s">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>14</v>
       </c>
       <c r="AI40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY40" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX40" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2192,11 +2165,17 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
+      <c r="AF41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>9</v>
+      </c>
       <c r="AH41" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="AI41" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AJ41" t="s">
         <v>14</v>
@@ -2205,12 +2184,9 @@
         <v>14</v>
       </c>
       <c r="AL41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM41" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ41" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY41" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2224,20 +2200,20 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AH42" t="s">
-        <v>5</v>
+      <c r="AF42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>9</v>
       </c>
       <c r="AI42" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AJ42" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="AL42" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="AM42" t="s">
         <v>14</v>
@@ -2246,12 +2222,9 @@
         <v>14</v>
       </c>
       <c r="AO42" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP42" t="s">
-        <v>21</v>
-      </c>
-      <c r="BA42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ42" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2265,17 +2238,23 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AH43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI43" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL43" t="s">
+      <c r="AF43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK43" t="s">
         <v>33</v>
       </c>
+      <c r="AO43" t="s">
+        <v>15</v>
+      </c>
       <c r="AP43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ43" t="s">
         <v>14</v>
@@ -2287,12 +2266,9 @@
         <v>14</v>
       </c>
       <c r="AT43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AU43" t="s">
-        <v>21</v>
-      </c>
-      <c r="BB43" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA43" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2306,14 +2282,17 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AH44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI44" t="s">
-        <v>9</v>
+      <c r="AF44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>34</v>
       </c>
       <c r="AL44" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AM44" t="s">
         <v>14</v>
@@ -2325,12 +2304,9 @@
         <v>14</v>
       </c>
       <c r="AP44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ44" t="s">
-        <v>21</v>
-      </c>
-      <c r="BC44" t="s">
+        <v>21</v>
+      </c>
+      <c r="BB44" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2344,14 +2320,17 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AI45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ45" t="s">
-        <v>9</v>
+      <c r="AG45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>34</v>
       </c>
       <c r="AM45" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AN45" t="s">
         <v>14</v>
@@ -2369,12 +2348,9 @@
         <v>14</v>
       </c>
       <c r="AS45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT45" t="s">
-        <v>21</v>
-      </c>
-      <c r="BD45" t="s">
+        <v>21</v>
+      </c>
+      <c r="BC45" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2388,22 +2364,22 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
+      <c r="AG46" t="s">
+        <v>5</v>
+      </c>
       <c r="AI46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ46" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>34</v>
       </c>
       <c r="AN46" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AO46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP46" t="s">
-        <v>21</v>
-      </c>
-      <c r="BE46" t="s">
+        <v>21</v>
+      </c>
+      <c r="BD46" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2417,22 +2393,22 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="AI47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK47" t="s">
-        <v>9</v>
+      <c r="AG47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>34</v>
       </c>
       <c r="AO47" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AP47" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ47" t="s">
-        <v>21</v>
-      </c>
-      <c r="BF47" t="s">
+        <v>21</v>
+      </c>
+      <c r="BE47" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2446,25 +2422,22 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
-      <c r="AI48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL48" t="s">
-        <v>9</v>
+      <c r="AG48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO48" t="s">
+        <v>34</v>
       </c>
       <c r="AP48" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AQ48" t="s">
-        <v>33</v>
-      </c>
-      <c r="AR48" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS48" t="s">
-        <v>21</v>
-      </c>
-      <c r="BG48" t="s">
+        <v>21</v>
+      </c>
+      <c r="BF48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2478,25 +2451,22 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-      <c r="AJ49" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN49" t="s">
-        <v>9</v>
+      <c r="AH49" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM49" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP49" t="s">
+        <v>34</v>
       </c>
       <c r="AQ49" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AR49" t="s">
-        <v>33</v>
-      </c>
-      <c r="AS49" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT49" t="s">
-        <v>21</v>
-      </c>
-      <c r="BH49" t="s">
+        <v>21</v>
+      </c>
+      <c r="BG49" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2510,20 +2480,23 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="AJ50" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP50" t="s">
-        <v>9</v>
+      <c r="AI50" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>34</v>
       </c>
       <c r="AR50" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AS50" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="AT50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU50" t="s">
         <v>14</v>
@@ -2535,12 +2508,9 @@
         <v>14</v>
       </c>
       <c r="AX50" t="s">
-        <v>14</v>
-      </c>
-      <c r="AY50" t="s">
-        <v>21</v>
-      </c>
-      <c r="BI50" t="s">
+        <v>21</v>
+      </c>
+      <c r="BH50" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2554,18 +2524,21 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="AK51" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ51" t="s">
-        <v>9</v>
+      <c r="AJ51" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>34</v>
       </c>
       <c r="AS51" t="s">
-        <v>34</v>
-      </c>
-      <c r="AT51" t="s">
         <v>33</v>
       </c>
+      <c r="AX51" t="s">
+        <v>14</v>
+      </c>
       <c r="AY51" t="s">
         <v>14</v>
       </c>
@@ -2573,12 +2546,9 @@
         <v>14</v>
       </c>
       <c r="BA51" t="s">
-        <v>14</v>
-      </c>
-      <c r="BB51" t="s">
-        <v>21</v>
-      </c>
-      <c r="BJ51" t="s">
+        <v>21</v>
+      </c>
+      <c r="BI51" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2592,25 +2562,25 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="AL52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ52" t="s">
-        <v>9</v>
+      <c r="AK52" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>34</v>
       </c>
       <c r="AT52" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU52" t="s">
         <v>33</v>
       </c>
+      <c r="BA52" t="s">
+        <v>14</v>
+      </c>
       <c r="BB52" t="s">
-        <v>14</v>
-      </c>
-      <c r="BC52" t="s">
-        <v>21</v>
-      </c>
-      <c r="BK52" t="s">
+        <v>21</v>
+      </c>
+      <c r="BJ52" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2624,25 +2594,22 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
-      <c r="AN53" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR53" t="s">
-        <v>9</v>
+      <c r="AM53" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT53" t="s">
+        <v>34</v>
       </c>
       <c r="AU53" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AV53" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW53" t="s">
-        <v>14</v>
-      </c>
-      <c r="AX53" t="s">
-        <v>21</v>
-      </c>
-      <c r="BL53" t="s">
+        <v>21</v>
+      </c>
+      <c r="BK53" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2656,25 +2623,22 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="AP54" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR54" t="s">
-        <v>9</v>
+      <c r="AO54" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>34</v>
       </c>
       <c r="AV54" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AW54" t="s">
-        <v>33</v>
-      </c>
-      <c r="AX54" t="s">
-        <v>14</v>
-      </c>
-      <c r="AY54" t="s">
-        <v>21</v>
-      </c>
-      <c r="BM54" t="s">
+        <v>21</v>
+      </c>
+      <c r="BL54" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2688,25 +2652,22 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="AQ55" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT55" t="s">
-        <v>9</v>
+      <c r="AP55" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>34</v>
       </c>
       <c r="AW55" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AX55" t="s">
-        <v>33</v>
-      </c>
-      <c r="AY55" t="s">
-        <v>14</v>
-      </c>
-      <c r="AZ55" t="s">
-        <v>21</v>
-      </c>
-      <c r="BN55" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2720,17 +2681,20 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
-      <c r="AQ56" t="s">
-        <v>5</v>
-      </c>
-      <c r="AV56" t="s">
-        <v>9</v>
+      <c r="AP56" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW56" t="s">
+        <v>34</v>
       </c>
       <c r="AX56" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AY56" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="AZ56" t="s">
         <v>14</v>
@@ -2739,15 +2703,9 @@
         <v>14</v>
       </c>
       <c r="BB56" t="s">
-        <v>14</v>
-      </c>
-      <c r="BC56" t="s">
-        <v>14</v>
-      </c>
-      <c r="BD56" t="s">
-        <v>21</v>
-      </c>
-      <c r="BO56" t="s">
+        <v>21</v>
+      </c>
+      <c r="BN56" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2761,31 +2719,31 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="AR57" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW57" t="s">
-        <v>9</v>
+      <c r="AQ57" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>9</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>34</v>
       </c>
       <c r="AY57" t="s">
-        <v>34</v>
-      </c>
-      <c r="AZ57" t="s">
         <v>33</v>
       </c>
+      <c r="BB57" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC57" t="s">
+        <v>14</v>
+      </c>
       <c r="BD57" t="s">
         <v>14</v>
       </c>
       <c r="BE57" t="s">
-        <v>14</v>
-      </c>
-      <c r="BF57" t="s">
-        <v>14</v>
-      </c>
-      <c r="BG57" t="s">
-        <v>21</v>
-      </c>
-      <c r="BP57" t="s">
+        <v>21</v>
+      </c>
+      <c r="BO57" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2799,25 +2757,25 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="AR58" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW58" t="s">
-        <v>9</v>
+      <c r="AQ58" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY58" t="s">
+        <v>34</v>
       </c>
       <c r="AZ58" t="s">
-        <v>34</v>
-      </c>
-      <c r="BA58" t="s">
         <v>33</v>
       </c>
-      <c r="BG58" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH58" t="s">
-        <v>21</v>
-      </c>
-      <c r="BQ58" t="s">
+      <c r="BE58" t="s">
+        <v>14</v>
+      </c>
+      <c r="BF58" t="s">
+        <v>21</v>
+      </c>
+      <c r="BP58" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2831,25 +2789,22 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="AT59" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX59" t="s">
-        <v>9</v>
+      <c r="AS59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW59" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ59" t="s">
+        <v>34</v>
       </c>
       <c r="BA59" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BB59" t="s">
-        <v>33</v>
-      </c>
-      <c r="BC59" t="s">
-        <v>14</v>
-      </c>
-      <c r="BD59" t="s">
-        <v>21</v>
-      </c>
-      <c r="BR59" t="s">
+        <v>21</v>
+      </c>
+      <c r="BQ59" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2863,25 +2818,22 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
-      <c r="AV60" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX60" t="s">
-        <v>9</v>
+      <c r="AU60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW60" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA60" t="s">
+        <v>34</v>
       </c>
       <c r="BB60" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BC60" t="s">
-        <v>33</v>
-      </c>
-      <c r="BD60" t="s">
-        <v>14</v>
-      </c>
-      <c r="BE60" t="s">
-        <v>21</v>
-      </c>
-      <c r="BS60" t="s">
+        <v>21</v>
+      </c>
+      <c r="BR60" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2895,25 +2847,22 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="AW61" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ61" t="s">
-        <v>9</v>
+      <c r="AV61" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY61" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB61" t="s">
+        <v>34</v>
       </c>
       <c r="BC61" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BD61" t="s">
-        <v>33</v>
-      </c>
-      <c r="BE61" t="s">
-        <v>14</v>
-      </c>
-      <c r="BF61" t="s">
-        <v>21</v>
-      </c>
-      <c r="BT61" t="s">
+        <v>21</v>
+      </c>
+      <c r="BS61" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2927,17 +2876,20 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="AW62" t="s">
-        <v>5</v>
-      </c>
-      <c r="BA62" t="s">
-        <v>9</v>
+      <c r="AV62" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ62" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC62" t="s">
+        <v>34</v>
       </c>
       <c r="BD62" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BE62" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BF62" t="s">
         <v>14</v>
@@ -2946,15 +2898,9 @@
         <v>14</v>
       </c>
       <c r="BH62" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI62" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ62" t="s">
-        <v>21</v>
-      </c>
-      <c r="BU62" t="s">
+        <v>21</v>
+      </c>
+      <c r="BT62" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2968,31 +2914,31 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
-      <c r="AX63" t="s">
-        <v>5</v>
-      </c>
-      <c r="BB63" t="s">
-        <v>9</v>
+      <c r="AW63" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA63" t="s">
+        <v>9</v>
+      </c>
+      <c r="BD63" t="s">
+        <v>34</v>
       </c>
       <c r="BE63" t="s">
-        <v>34</v>
-      </c>
-      <c r="BF63" t="s">
         <v>33</v>
       </c>
+      <c r="BH63" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI63" t="s">
+        <v>14</v>
+      </c>
       <c r="BJ63" t="s">
         <v>14</v>
       </c>
       <c r="BK63" t="s">
-        <v>14</v>
-      </c>
-      <c r="BL63" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM63" t="s">
-        <v>21</v>
-      </c>
-      <c r="BV63" t="s">
+        <v>21</v>
+      </c>
+      <c r="BU63" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3006,25 +2952,25 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="AX64" t="s">
-        <v>5</v>
-      </c>
-      <c r="BB64" t="s">
-        <v>9</v>
+      <c r="AW64" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA64" t="s">
+        <v>9</v>
+      </c>
+      <c r="BE64" t="s">
+        <v>34</v>
       </c>
       <c r="BF64" t="s">
-        <v>34</v>
-      </c>
-      <c r="BG64" t="s">
         <v>33</v>
       </c>
-      <c r="BM64" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN64" t="s">
-        <v>21</v>
-      </c>
-      <c r="BW64" t="s">
+      <c r="BK64" t="s">
+        <v>14</v>
+      </c>
+      <c r="BL64" t="s">
+        <v>21</v>
+      </c>
+      <c r="BV64" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3038,25 +2984,22 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
-      <c r="AZ65" t="s">
-        <v>5</v>
-      </c>
-      <c r="BC65" t="s">
-        <v>9</v>
+      <c r="AY65" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB65" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF65" t="s">
+        <v>34</v>
       </c>
       <c r="BG65" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BH65" t="s">
-        <v>33</v>
-      </c>
-      <c r="BI65" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ65" t="s">
-        <v>21</v>
-      </c>
-      <c r="BX65" t="s">
+        <v>21</v>
+      </c>
+      <c r="BW65" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3070,25 +3013,22 @@
       <c r="C66" t="s">
         <v>32</v>
       </c>
-      <c r="BA66" t="s">
-        <v>5</v>
-      </c>
-      <c r="BC66" t="s">
-        <v>9</v>
+      <c r="AZ66" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB66" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG66" t="s">
+        <v>34</v>
       </c>
       <c r="BH66" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BI66" t="s">
-        <v>33</v>
-      </c>
-      <c r="BJ66" t="s">
-        <v>14</v>
-      </c>
-      <c r="BK66" t="s">
-        <v>21</v>
-      </c>
-      <c r="BY66" t="s">
+        <v>21</v>
+      </c>
+      <c r="BX66" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3102,25 +3042,25 @@
       <c r="C67" t="s">
         <v>35</v>
       </c>
+      <c r="BI67" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ67" t="s">
+        <v>9</v>
+      </c>
       <c r="BK67" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BL67" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BM67" t="s">
         <v>14</v>
       </c>
       <c r="BN67" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO67" t="s">
-        <v>14</v>
-      </c>
-      <c r="BP67" t="s">
-        <v>21</v>
-      </c>
-      <c r="BZ67" t="s">
+        <v>21</v>
+      </c>
+      <c r="BY67" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3134,28 +3074,28 @@
       <c r="C68" t="s">
         <v>36</v>
       </c>
+      <c r="BI68" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ68" t="s">
+        <v>9</v>
+      </c>
       <c r="BK68" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL68" t="s">
-        <v>9</v>
-      </c>
-      <c r="BM68" t="s">
         <v>33</v>
       </c>
+      <c r="BN68" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO68" t="s">
+        <v>14</v>
+      </c>
       <c r="BP68" t="s">
         <v>14</v>
       </c>
       <c r="BQ68" t="s">
-        <v>14</v>
-      </c>
-      <c r="BR68" t="s">
-        <v>14</v>
-      </c>
-      <c r="BS68" t="s">
-        <v>21</v>
-      </c>
-      <c r="CA68" t="s">
+        <v>21</v>
+      </c>
+      <c r="BZ68" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3169,19 +3109,19 @@
       <c r="C69" t="s">
         <v>37</v>
       </c>
+      <c r="BI69" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ69" t="s">
+        <v>9</v>
+      </c>
       <c r="BK69" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BL69" t="s">
-        <v>9</v>
-      </c>
-      <c r="BM69" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN69" t="s">
-        <v>21</v>
-      </c>
-      <c r="CB69" t="s">
+        <v>21</v>
+      </c>
+      <c r="CA69" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3195,19 +3135,22 @@
       <c r="C70" t="s">
         <v>38</v>
       </c>
+      <c r="BI70" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ70" t="s">
+        <v>9</v>
+      </c>
       <c r="BK70" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BL70" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BM70" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN70" t="s">
-        <v>21</v>
-      </c>
-      <c r="CC70" t="s">
+        <v>21</v>
+      </c>
+      <c r="CB70" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3221,11 +3164,17 @@
       <c r="C71" t="s">
         <v>18</v>
       </c>
+      <c r="BJ71" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK71" t="s">
+        <v>9</v>
+      </c>
       <c r="BL71" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BM71" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BN71" t="s">
         <v>14</v>
@@ -3234,12 +3183,9 @@
         <v>14</v>
       </c>
       <c r="BP71" t="s">
-        <v>14</v>
-      </c>
-      <c r="BQ71" t="s">
-        <v>21</v>
-      </c>
-      <c r="CD71" t="s">
+        <v>21</v>
+      </c>
+      <c r="CC71" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3253,20 +3199,20 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
-      <c r="BL72" t="s">
-        <v>5</v>
+      <c r="BJ72" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK72" t="s">
+        <v>9</v>
       </c>
       <c r="BM72" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BN72" t="s">
-        <v>16</v>
-      </c>
-      <c r="BO72" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="BP72" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BQ72" t="s">
         <v>14</v>
@@ -3275,12 +3221,9 @@
         <v>14</v>
       </c>
       <c r="BS72" t="s">
-        <v>14</v>
-      </c>
-      <c r="BT72" t="s">
-        <v>21</v>
-      </c>
-      <c r="CE72" t="s">
+        <v>21</v>
+      </c>
+      <c r="CD72" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3294,17 +3237,23 @@
       <c r="C73" t="s">
         <v>20</v>
       </c>
-      <c r="BL73" t="s">
-        <v>5</v>
-      </c>
-      <c r="BM73" t="s">
-        <v>9</v>
-      </c>
-      <c r="BP73" t="s">
+      <c r="BJ73" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK73" t="s">
+        <v>9</v>
+      </c>
+      <c r="BN73" t="s">
+        <v>34</v>
+      </c>
+      <c r="BO73" t="s">
         <v>33</v>
       </c>
+      <c r="BS73" t="s">
+        <v>15</v>
+      </c>
       <c r="BT73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BU73" t="s">
         <v>14</v>
@@ -3316,12 +3265,9 @@
         <v>14</v>
       </c>
       <c r="BX73" t="s">
-        <v>14</v>
-      </c>
-      <c r="BY73" t="s">
-        <v>21</v>
-      </c>
-      <c r="CF73" t="s">
+        <v>21</v>
+      </c>
+      <c r="CE73" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3335,14 +3281,17 @@
       <c r="C74" t="s">
         <v>23</v>
       </c>
-      <c r="BL74" t="s">
-        <v>5</v>
-      </c>
-      <c r="BM74" t="s">
-        <v>9</v>
+      <c r="BJ74" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK74" t="s">
+        <v>9</v>
+      </c>
+      <c r="BO74" t="s">
+        <v>34</v>
       </c>
       <c r="BP74" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BQ74" t="s">
         <v>14</v>
@@ -3354,12 +3303,9 @@
         <v>14</v>
       </c>
       <c r="BT74" t="s">
-        <v>14</v>
-      </c>
-      <c r="BU74" t="s">
-        <v>21</v>
-      </c>
-      <c r="CG74" t="s">
+        <v>21</v>
+      </c>
+      <c r="CF74" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3373,14 +3319,17 @@
       <c r="C75" t="s">
         <v>24</v>
       </c>
-      <c r="BM75" t="s">
-        <v>5</v>
-      </c>
-      <c r="BN75" t="s">
-        <v>9</v>
+      <c r="BK75" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL75" t="s">
+        <v>9</v>
+      </c>
+      <c r="BP75" t="s">
+        <v>34</v>
       </c>
       <c r="BQ75" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BR75" t="s">
         <v>14</v>
@@ -3398,12 +3347,9 @@
         <v>14</v>
       </c>
       <c r="BW75" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX75" t="s">
-        <v>21</v>
-      </c>
-      <c r="CH75" t="s">
+        <v>21</v>
+      </c>
+      <c r="CG75" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3417,22 +3363,22 @@
       <c r="C76" t="s">
         <v>25</v>
       </c>
+      <c r="BK76" t="s">
+        <v>5</v>
+      </c>
       <c r="BM76" t="s">
-        <v>5</v>
-      </c>
-      <c r="BN76" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BQ76" t="s">
+        <v>34</v>
       </c>
       <c r="BR76" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BS76" t="s">
-        <v>14</v>
-      </c>
-      <c r="BT76" t="s">
-        <v>21</v>
-      </c>
-      <c r="CI76" t="s">
+        <v>21</v>
+      </c>
+      <c r="CH76" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3446,22 +3392,22 @@
       <c r="C77" t="s">
         <v>13</v>
       </c>
-      <c r="BM77" t="s">
-        <v>5</v>
-      </c>
-      <c r="BO77" t="s">
-        <v>9</v>
+      <c r="BK77" t="s">
+        <v>5</v>
+      </c>
+      <c r="BN77" t="s">
+        <v>9</v>
+      </c>
+      <c r="BR77" t="s">
+        <v>34</v>
       </c>
       <c r="BS77" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BT77" t="s">
-        <v>14</v>
-      </c>
-      <c r="BU77" t="s">
-        <v>21</v>
-      </c>
-      <c r="CJ77" t="s">
+        <v>21</v>
+      </c>
+      <c r="CI77" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3475,25 +3421,22 @@
       <c r="C78" t="s">
         <v>26</v>
       </c>
-      <c r="BM78" t="s">
-        <v>5</v>
-      </c>
-      <c r="BP78" t="s">
-        <v>9</v>
+      <c r="BK78" t="s">
+        <v>5</v>
+      </c>
+      <c r="BO78" t="s">
+        <v>9</v>
+      </c>
+      <c r="BS78" t="s">
+        <v>34</v>
       </c>
       <c r="BT78" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BU78" t="s">
-        <v>33</v>
-      </c>
-      <c r="BV78" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW78" t="s">
-        <v>21</v>
-      </c>
-      <c r="CK78" t="s">
+        <v>21</v>
+      </c>
+      <c r="CJ78" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3507,25 +3450,22 @@
       <c r="C79" t="s">
         <v>27</v>
       </c>
-      <c r="BN79" t="s">
-        <v>5</v>
-      </c>
-      <c r="BR79" t="s">
-        <v>9</v>
+      <c r="BL79" t="s">
+        <v>5</v>
+      </c>
+      <c r="BQ79" t="s">
+        <v>9</v>
+      </c>
+      <c r="BT79" t="s">
+        <v>34</v>
       </c>
       <c r="BU79" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BV79" t="s">
-        <v>33</v>
-      </c>
-      <c r="BW79" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX79" t="s">
-        <v>21</v>
-      </c>
-      <c r="CL79" t="s">
+        <v>21</v>
+      </c>
+      <c r="CK79" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3539,20 +3479,23 @@
       <c r="C80" t="s">
         <v>28</v>
       </c>
-      <c r="BN80" t="s">
-        <v>5</v>
-      </c>
-      <c r="BT80" t="s">
-        <v>9</v>
+      <c r="BM80" t="s">
+        <v>5</v>
+      </c>
+      <c r="BS80" t="s">
+        <v>9</v>
+      </c>
+      <c r="BU80" t="s">
+        <v>34</v>
       </c>
       <c r="BV80" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="BW80" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="BX80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BY80" t="s">
         <v>14</v>
@@ -3564,12 +3507,9 @@
         <v>14</v>
       </c>
       <c r="CB80" t="s">
-        <v>14</v>
-      </c>
-      <c r="CC80" t="s">
-        <v>21</v>
-      </c>
-      <c r="CM80" t="s">
+        <v>21</v>
+      </c>
+      <c r="CL80" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3583,18 +3523,21 @@
       <c r="C81" t="s">
         <v>29</v>
       </c>
-      <c r="BO81" t="s">
-        <v>5</v>
-      </c>
-      <c r="BU81" t="s">
-        <v>9</v>
+      <c r="BN81" t="s">
+        <v>5</v>
+      </c>
+      <c r="BT81" t="s">
+        <v>9</v>
+      </c>
+      <c r="BV81" t="s">
+        <v>34</v>
       </c>
       <c r="BW81" t="s">
-        <v>34</v>
-      </c>
-      <c r="BX81" t="s">
         <v>33</v>
       </c>
+      <c r="CB81" t="s">
+        <v>14</v>
+      </c>
       <c r="CC81" t="s">
         <v>14</v>
       </c>
@@ -3602,12 +3545,9 @@
         <v>14</v>
       </c>
       <c r="CE81" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF81" t="s">
-        <v>21</v>
-      </c>
-      <c r="CN81" t="s">
+        <v>21</v>
+      </c>
+      <c r="CM81" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3621,25 +3561,25 @@
       <c r="C82" t="s">
         <v>30</v>
       </c>
-      <c r="BP82" t="s">
-        <v>5</v>
-      </c>
-      <c r="BU82" t="s">
-        <v>9</v>
+      <c r="BO82" t="s">
+        <v>5</v>
+      </c>
+      <c r="BT82" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW82" t="s">
+        <v>34</v>
       </c>
       <c r="BX82" t="s">
-        <v>34</v>
-      </c>
-      <c r="BY82" t="s">
         <v>33</v>
       </c>
+      <c r="CE82" t="s">
+        <v>14</v>
+      </c>
       <c r="CF82" t="s">
-        <v>14</v>
-      </c>
-      <c r="CG82" t="s">
-        <v>21</v>
-      </c>
-      <c r="CO82" t="s">
+        <v>21</v>
+      </c>
+      <c r="CN82" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3653,25 +3593,22 @@
       <c r="C83" t="s">
         <v>31</v>
       </c>
-      <c r="BR83" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV83" t="s">
-        <v>9</v>
+      <c r="BQ83" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU83" t="s">
+        <v>9</v>
+      </c>
+      <c r="BX83" t="s">
+        <v>34</v>
       </c>
       <c r="BY83" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BZ83" t="s">
-        <v>33</v>
-      </c>
-      <c r="CA83" t="s">
-        <v>14</v>
-      </c>
-      <c r="CB83" t="s">
-        <v>21</v>
-      </c>
-      <c r="CP83" t="s">
+        <v>21</v>
+      </c>
+      <c r="CO83" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3685,25 +3622,22 @@
       <c r="C84" t="s">
         <v>32</v>
       </c>
-      <c r="BT84" t="s">
-        <v>5</v>
-      </c>
-      <c r="BV84" t="s">
-        <v>9</v>
+      <c r="BS84" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU84" t="s">
+        <v>9</v>
+      </c>
+      <c r="BY84" t="s">
+        <v>34</v>
       </c>
       <c r="BZ84" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CA84" t="s">
-        <v>33</v>
-      </c>
-      <c r="CB84" t="s">
-        <v>14</v>
-      </c>
-      <c r="CC84" t="s">
-        <v>21</v>
-      </c>
-      <c r="CQ84" t="s">
+        <v>21</v>
+      </c>
+      <c r="CP84" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3717,25 +3651,22 @@
       <c r="C85" t="s">
         <v>27</v>
       </c>
-      <c r="BU85" t="s">
-        <v>5</v>
-      </c>
-      <c r="BX85" t="s">
-        <v>9</v>
+      <c r="BT85" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW85" t="s">
+        <v>9</v>
+      </c>
+      <c r="BZ85" t="s">
+        <v>34</v>
       </c>
       <c r="CA85" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CB85" t="s">
-        <v>33</v>
-      </c>
-      <c r="CC85" t="s">
-        <v>14</v>
-      </c>
-      <c r="CD85" t="s">
-        <v>21</v>
-      </c>
-      <c r="CR85" t="s">
+        <v>21</v>
+      </c>
+      <c r="CQ85" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3749,17 +3680,20 @@
       <c r="C86" t="s">
         <v>28</v>
       </c>
-      <c r="BU86" t="s">
-        <v>5</v>
-      </c>
-      <c r="BZ86" t="s">
-        <v>9</v>
+      <c r="BT86" t="s">
+        <v>5</v>
+      </c>
+      <c r="BY86" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA86" t="s">
+        <v>34</v>
       </c>
       <c r="CB86" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CC86" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CD86" t="s">
         <v>14</v>
@@ -3768,15 +3702,9 @@
         <v>14</v>
       </c>
       <c r="CF86" t="s">
-        <v>14</v>
-      </c>
-      <c r="CG86" t="s">
-        <v>14</v>
-      </c>
-      <c r="CH86" t="s">
-        <v>21</v>
-      </c>
-      <c r="CS86" t="s">
+        <v>21</v>
+      </c>
+      <c r="CR86" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3790,31 +3718,31 @@
       <c r="C87" t="s">
         <v>29</v>
       </c>
-      <c r="BV87" t="s">
-        <v>5</v>
-      </c>
-      <c r="CA87" t="s">
-        <v>9</v>
+      <c r="BU87" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ87" t="s">
+        <v>9</v>
+      </c>
+      <c r="CB87" t="s">
+        <v>34</v>
       </c>
       <c r="CC87" t="s">
-        <v>34</v>
-      </c>
-      <c r="CD87" t="s">
         <v>33</v>
       </c>
+      <c r="CF87" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG87" t="s">
+        <v>14</v>
+      </c>
       <c r="CH87" t="s">
         <v>14</v>
       </c>
       <c r="CI87" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ87" t="s">
-        <v>14</v>
-      </c>
-      <c r="CK87" t="s">
-        <v>21</v>
-      </c>
-      <c r="CT87" t="s">
+        <v>21</v>
+      </c>
+      <c r="CS87" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3828,25 +3756,25 @@
       <c r="C88" t="s">
         <v>30</v>
       </c>
-      <c r="BV88" t="s">
-        <v>5</v>
-      </c>
-      <c r="CA88" t="s">
-        <v>9</v>
+      <c r="BU88" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ88" t="s">
+        <v>9</v>
+      </c>
+      <c r="CC88" t="s">
+        <v>34</v>
       </c>
       <c r="CD88" t="s">
-        <v>34</v>
-      </c>
-      <c r="CE88" t="s">
         <v>33</v>
       </c>
-      <c r="CK88" t="s">
-        <v>14</v>
-      </c>
-      <c r="CL88" t="s">
-        <v>21</v>
-      </c>
-      <c r="CU88" t="s">
+      <c r="CI88" t="s">
+        <v>14</v>
+      </c>
+      <c r="CJ88" t="s">
+        <v>21</v>
+      </c>
+      <c r="CT88" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3860,25 +3788,22 @@
       <c r="C89" t="s">
         <v>31</v>
       </c>
-      <c r="BX89" t="s">
-        <v>5</v>
-      </c>
-      <c r="CB89" t="s">
-        <v>9</v>
+      <c r="BW89" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA89" t="s">
+        <v>9</v>
+      </c>
+      <c r="CD89" t="s">
+        <v>34</v>
       </c>
       <c r="CE89" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CF89" t="s">
-        <v>33</v>
-      </c>
-      <c r="CG89" t="s">
-        <v>14</v>
-      </c>
-      <c r="CH89" t="s">
-        <v>21</v>
-      </c>
-      <c r="CV89" t="s">
+        <v>21</v>
+      </c>
+      <c r="CU89" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3892,25 +3817,22 @@
       <c r="C90" t="s">
         <v>32</v>
       </c>
-      <c r="BZ90" t="s">
-        <v>5</v>
-      </c>
-      <c r="CB90" t="s">
-        <v>9</v>
+      <c r="BY90" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA90" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE90" t="s">
+        <v>34</v>
       </c>
       <c r="CF90" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CG90" t="s">
-        <v>33</v>
-      </c>
-      <c r="CH90" t="s">
-        <v>14</v>
-      </c>
-      <c r="CI90" t="s">
-        <v>21</v>
-      </c>
-      <c r="CW90" t="s">
+        <v>21</v>
+      </c>
+      <c r="CV90" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3924,25 +3846,22 @@
       <c r="C91" t="s">
         <v>27</v>
       </c>
-      <c r="CA91" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD91" t="s">
-        <v>9</v>
+      <c r="BZ91" t="s">
+        <v>5</v>
+      </c>
+      <c r="CC91" t="s">
+        <v>9</v>
+      </c>
+      <c r="CF91" t="s">
+        <v>34</v>
       </c>
       <c r="CG91" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CH91" t="s">
-        <v>33</v>
-      </c>
-      <c r="CI91" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ91" t="s">
-        <v>21</v>
-      </c>
-      <c r="CX91" t="s">
+        <v>21</v>
+      </c>
+      <c r="CW91" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3956,17 +3875,20 @@
       <c r="C92" t="s">
         <v>28</v>
       </c>
-      <c r="CA92" t="s">
-        <v>5</v>
-      </c>
-      <c r="CE92" t="s">
-        <v>9</v>
+      <c r="BZ92" t="s">
+        <v>5</v>
+      </c>
+      <c r="CD92" t="s">
+        <v>9</v>
+      </c>
+      <c r="CG92" t="s">
+        <v>34</v>
       </c>
       <c r="CH92" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CI92" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CJ92" t="s">
         <v>14</v>
@@ -3975,15 +3897,9 @@
         <v>14</v>
       </c>
       <c r="CL92" t="s">
-        <v>14</v>
-      </c>
-      <c r="CM92" t="s">
-        <v>14</v>
-      </c>
-      <c r="CN92" t="s">
-        <v>21</v>
-      </c>
-      <c r="CY92" t="s">
+        <v>21</v>
+      </c>
+      <c r="CX92" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3997,31 +3913,31 @@
       <c r="C93" t="s">
         <v>29</v>
       </c>
-      <c r="CB93" t="s">
-        <v>5</v>
-      </c>
-      <c r="CF93" t="s">
-        <v>9</v>
+      <c r="CA93" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE93" t="s">
+        <v>9</v>
+      </c>
+      <c r="CH93" t="s">
+        <v>34</v>
       </c>
       <c r="CI93" t="s">
-        <v>34</v>
-      </c>
-      <c r="CJ93" t="s">
         <v>33</v>
       </c>
+      <c r="CL93" t="s">
+        <v>14</v>
+      </c>
+      <c r="CM93" t="s">
+        <v>14</v>
+      </c>
       <c r="CN93" t="s">
         <v>14</v>
       </c>
       <c r="CO93" t="s">
-        <v>14</v>
-      </c>
-      <c r="CP93" t="s">
-        <v>14</v>
-      </c>
-      <c r="CQ93" t="s">
-        <v>21</v>
-      </c>
-      <c r="CZ93" t="s">
+        <v>21</v>
+      </c>
+      <c r="CY93" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4035,25 +3951,25 @@
       <c r="C94" t="s">
         <v>30</v>
       </c>
-      <c r="CB94" t="s">
-        <v>5</v>
-      </c>
-      <c r="CF94" t="s">
-        <v>9</v>
+      <c r="CA94" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE94" t="s">
+        <v>9</v>
+      </c>
+      <c r="CI94" t="s">
+        <v>34</v>
       </c>
       <c r="CJ94" t="s">
-        <v>34</v>
-      </c>
-      <c r="CK94" t="s">
         <v>33</v>
       </c>
-      <c r="CQ94" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR94" t="s">
-        <v>21</v>
-      </c>
-      <c r="DA94" t="s">
+      <c r="CO94" t="s">
+        <v>14</v>
+      </c>
+      <c r="CP94" t="s">
+        <v>21</v>
+      </c>
+      <c r="CZ94" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4067,25 +3983,22 @@
       <c r="C95" t="s">
         <v>31</v>
       </c>
-      <c r="CD95" t="s">
-        <v>5</v>
-      </c>
-      <c r="CG95" t="s">
-        <v>9</v>
+      <c r="CC95" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF95" t="s">
+        <v>9</v>
+      </c>
+      <c r="CJ95" t="s">
+        <v>34</v>
       </c>
       <c r="CK95" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CL95" t="s">
-        <v>33</v>
-      </c>
-      <c r="CM95" t="s">
-        <v>14</v>
-      </c>
-      <c r="CN95" t="s">
-        <v>21</v>
-      </c>
-      <c r="DB95" t="s">
+        <v>21</v>
+      </c>
+      <c r="DA95" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4099,25 +4012,22 @@
       <c r="C96" t="s">
         <v>32</v>
       </c>
-      <c r="CE96" t="s">
-        <v>5</v>
-      </c>
-      <c r="CG96" t="s">
-        <v>9</v>
+      <c r="CD96" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF96" t="s">
+        <v>9</v>
+      </c>
+      <c r="CK96" t="s">
+        <v>34</v>
       </c>
       <c r="CL96" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CM96" t="s">
-        <v>33</v>
-      </c>
-      <c r="CN96" t="s">
-        <v>14</v>
-      </c>
-      <c r="CO96" t="s">
-        <v>21</v>
-      </c>
-      <c r="DC96" t="s">
+        <v>21</v>
+      </c>
+      <c r="DB96" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4131,25 +4041,25 @@
       <c r="C97" t="s">
         <v>35</v>
       </c>
+      <c r="CM97" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN97" t="s">
+        <v>9</v>
+      </c>
       <c r="CO97" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CP97" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CQ97" t="s">
         <v>14</v>
       </c>
       <c r="CR97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CS97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT97" t="s">
-        <v>21</v>
-      </c>
-      <c r="DD97" t="s">
+        <v>21</v>
+      </c>
+      <c r="DC97" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4163,28 +4073,28 @@
       <c r="C98" t="s">
         <v>36</v>
       </c>
+      <c r="CM98" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN98" t="s">
+        <v>9</v>
+      </c>
       <c r="CO98" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP98" t="s">
-        <v>9</v>
-      </c>
-      <c r="CQ98" t="s">
         <v>33</v>
       </c>
+      <c r="CR98" t="s">
+        <v>14</v>
+      </c>
+      <c r="CS98" t="s">
+        <v>14</v>
+      </c>
       <c r="CT98" t="s">
         <v>14</v>
       </c>
       <c r="CU98" t="s">
-        <v>14</v>
-      </c>
-      <c r="CV98" t="s">
-        <v>14</v>
-      </c>
-      <c r="CW98" t="s">
-        <v>21</v>
-      </c>
-      <c r="DE98" t="s">
+        <v>21</v>
+      </c>
+      <c r="DD98" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4198,19 +4108,19 @@
       <c r="C99" t="s">
         <v>37</v>
       </c>
+      <c r="CM99" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN99" t="s">
+        <v>9</v>
+      </c>
       <c r="CO99" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CP99" t="s">
-        <v>9</v>
-      </c>
-      <c r="CQ99" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR99" t="s">
-        <v>21</v>
-      </c>
-      <c r="DF99" t="s">
+        <v>21</v>
+      </c>
+      <c r="DE99" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4224,16 +4134,19 @@
       <c r="C100" t="s">
         <v>38</v>
       </c>
+      <c r="CM100" t="s">
+        <v>5</v>
+      </c>
       <c r="CO100" t="s">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="CP100" t="s">
+        <v>14</v>
       </c>
       <c r="CQ100" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR100" t="s">
-        <v>21</v>
-      </c>
-      <c r="DG100" t="s">
+        <v>21</v>
+      </c>
+      <c r="DF100" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4247,19 +4160,22 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
+      <c r="CN101" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO101" t="s">
+        <v>9</v>
+      </c>
       <c r="CP101" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="CQ101" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CR101" t="s">
-        <v>14</v>
-      </c>
-      <c r="CS101" t="s">
-        <v>21</v>
-      </c>
-      <c r="DH101" t="s">
+        <v>21</v>
+      </c>
+      <c r="DG101" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4273,22 +4189,22 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="CP102" t="s">
-        <v>5</v>
+      <c r="CN102" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO102" t="s">
+        <v>9</v>
       </c>
       <c r="CQ102" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="CR102" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CS102" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT102" t="s">
-        <v>21</v>
-      </c>
-      <c r="DI102" t="s">
+        <v>21</v>
+      </c>
+      <c r="DH102" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4302,22 +4218,22 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="CP103" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ103" t="s">
-        <v>9</v>
+      <c r="CN103" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO103" t="s">
+        <v>9</v>
+      </c>
+      <c r="CR103" t="s">
+        <v>34</v>
       </c>
       <c r="CS103" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CT103" t="s">
-        <v>14</v>
-      </c>
-      <c r="CU103" t="s">
-        <v>21</v>
-      </c>
-      <c r="DJ103" t="s">
+        <v>21</v>
+      </c>
+      <c r="DI103" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4331,22 +4247,22 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
-      <c r="CP104" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ104" t="s">
-        <v>9</v>
+      <c r="CN104" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO104" t="s">
+        <v>9</v>
+      </c>
+      <c r="CS104" t="s">
+        <v>34</v>
       </c>
       <c r="CT104" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CU104" t="s">
-        <v>14</v>
-      </c>
-      <c r="CV104" t="s">
-        <v>21</v>
-      </c>
-      <c r="DK104" t="s">
+        <v>21</v>
+      </c>
+      <c r="DJ104" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4360,22 +4276,22 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
-      <c r="CQ105" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR105" t="s">
-        <v>9</v>
+      <c r="CO105" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP105" t="s">
+        <v>9</v>
+      </c>
+      <c r="CT105" t="s">
+        <v>34</v>
       </c>
       <c r="CU105" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CV105" t="s">
-        <v>14</v>
-      </c>
-      <c r="CW105" t="s">
-        <v>21</v>
-      </c>
-      <c r="DL105" t="s">
+        <v>21</v>
+      </c>
+      <c r="DK105" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4389,25 +4305,22 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
-      <c r="CQ106" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR106" t="s">
-        <v>9</v>
+      <c r="CO106" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP106" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU106" t="s">
+        <v>34</v>
       </c>
       <c r="CV106" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CW106" t="s">
-        <v>33</v>
-      </c>
-      <c r="CX106" t="s">
-        <v>14</v>
-      </c>
-      <c r="CY106" t="s">
-        <v>21</v>
-      </c>
-      <c r="DM106" t="s">
+        <v>21</v>
+      </c>
+      <c r="DL106" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4421,25 +4334,22 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
-      <c r="CQ107" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR107" t="s">
-        <v>9</v>
+      <c r="CO107" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP107" t="s">
+        <v>9</v>
+      </c>
+      <c r="CV107" t="s">
+        <v>34</v>
       </c>
       <c r="CW107" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CX107" t="s">
-        <v>15</v>
-      </c>
-      <c r="CY107" t="s">
-        <v>14</v>
-      </c>
-      <c r="CZ107" t="s">
-        <v>21</v>
-      </c>
-      <c r="DN107" t="s">
+        <v>21</v>
+      </c>
+      <c r="DM107" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4453,25 +4363,22 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
-      <c r="CQ108" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR108" t="s">
-        <v>9</v>
+      <c r="CO108" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP108" t="s">
+        <v>9</v>
+      </c>
+      <c r="CW108" t="s">
+        <v>34</v>
       </c>
       <c r="CX108" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CY108" t="s">
-        <v>33</v>
-      </c>
-      <c r="CZ108" t="s">
-        <v>14</v>
-      </c>
-      <c r="DA108" t="s">
-        <v>21</v>
-      </c>
-      <c r="DO108" t="s">
+        <v>21</v>
+      </c>
+      <c r="DN108" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4485,25 +4392,22 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
-      <c r="CR109" t="s">
-        <v>5</v>
-      </c>
-      <c r="CS109" t="s">
-        <v>9</v>
+      <c r="CP109" t="s">
+        <v>5</v>
+      </c>
+      <c r="CQ109" t="s">
+        <v>9</v>
+      </c>
+      <c r="CX109" t="s">
+        <v>34</v>
       </c>
       <c r="CY109" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CZ109" t="s">
-        <v>33</v>
-      </c>
-      <c r="DA109" t="s">
-        <v>14</v>
-      </c>
-      <c r="DB109" t="s">
-        <v>21</v>
-      </c>
-      <c r="DP109" t="s">
+        <v>21</v>
+      </c>
+      <c r="DO109" t="s">
         <v>22</v>
       </c>
     </row>

--- a/project/outputs_xlsx_solution/test33.4-wide-NC-1.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NC-1.xlsx
@@ -2142,6 +2142,9 @@
       <c r="AE40" t="s">
         <v>5</v>
       </c>
+      <c r="AF40" t="s">
+        <v>9</v>
+      </c>
       <c r="AG40" t="s">
         <v>34</v>
       </c>
@@ -2165,25 +2168,22 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="AF41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>34</v>
-      </c>
       <c r="AI41" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AJ41" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AK41" t="s">
         <v>14</v>
       </c>
       <c r="AL41" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN41" t="s">
         <v>21</v>
       </c>
       <c r="AY41" t="s">
@@ -2200,28 +2200,25 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AF42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>9</v>
-      </c>
       <c r="AI42" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AJ42" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK42" t="s">
         <v>33</v>
       </c>
-      <c r="AL42" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM42" t="s">
-        <v>14</v>
-      </c>
       <c r="AN42" t="s">
         <v>14</v>
       </c>
       <c r="AO42" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ42" t="s">
         <v>21</v>
       </c>
       <c r="AZ42" t="s">
@@ -2238,24 +2235,15 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AF43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" t="s">
-        <v>9</v>
+      <c r="AI43" t="s">
+        <v>5</v>
       </c>
       <c r="AJ43" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="AK43" t="s">
         <v>33</v>
       </c>
-      <c r="AO43" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP43" t="s">
-        <v>14</v>
-      </c>
       <c r="AQ43" t="s">
         <v>14</v>
       </c>
@@ -2266,6 +2254,9 @@
         <v>14</v>
       </c>
       <c r="AT43" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU43" t="s">
         <v>21</v>
       </c>
       <c r="BA43" t="s">
@@ -2282,10 +2273,10 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AF44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" t="s">
+      <c r="AI44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" t="s">
         <v>9</v>
       </c>
       <c r="AK44" t="s">
@@ -2320,10 +2311,10 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AG45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH45" t="s">
+      <c r="AJ45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" t="s">
         <v>9</v>
       </c>
       <c r="AL45" t="s">
@@ -2364,10 +2355,10 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AG46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI46" t="s">
+      <c r="AJ46" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" t="s">
         <v>9</v>
       </c>
       <c r="AM46" t="s">
@@ -2393,10 +2384,10 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="AG47" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" t="s">
         <v>9</v>
       </c>
       <c r="AN47" t="s">
@@ -2422,7 +2413,7 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
-      <c r="AG48" t="s">
+      <c r="AJ48" t="s">
         <v>5</v>
       </c>
       <c r="AK48" t="s">
@@ -2451,7 +2442,7 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-      <c r="AH49" t="s">
+      <c r="AK49" t="s">
         <v>5</v>
       </c>
       <c r="AM49" t="s">
@@ -2480,7 +2471,7 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="AI50" t="s">
+      <c r="AK50" t="s">
         <v>5</v>
       </c>
       <c r="AO50" t="s">
@@ -2496,7 +2487,7 @@
         <v>15</v>
       </c>
       <c r="AT50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU50" t="s">
         <v>14</v>
@@ -2508,6 +2499,9 @@
         <v>14</v>
       </c>
       <c r="AX50" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY50" t="s">
         <v>21</v>
       </c>
       <c r="BH50" t="s">
@@ -2524,7 +2518,7 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="AJ51" t="s">
+      <c r="AK51" t="s">
         <v>5</v>
       </c>
       <c r="AP51" t="s">
@@ -2536,9 +2530,6 @@
       <c r="AS51" t="s">
         <v>33</v>
       </c>
-      <c r="AX51" t="s">
-        <v>14</v>
-      </c>
       <c r="AY51" t="s">
         <v>14</v>
       </c>
@@ -2546,6 +2537,9 @@
         <v>14</v>
       </c>
       <c r="BA51" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB51" t="s">
         <v>21</v>
       </c>
       <c r="BI51" t="s">
@@ -2574,10 +2568,10 @@
       <c r="AT52" t="s">
         <v>33</v>
       </c>
-      <c r="BA52" t="s">
-        <v>14</v>
-      </c>
       <c r="BB52" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC52" t="s">
         <v>21</v>
       </c>
       <c r="BJ52" t="s">
@@ -2691,7 +2685,7 @@
         <v>34</v>
       </c>
       <c r="AX56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY56" t="s">
         <v>14</v>
@@ -2703,6 +2697,9 @@
         <v>14</v>
       </c>
       <c r="BB56" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC56" t="s">
         <v>21</v>
       </c>
       <c r="BN56" t="s">
@@ -2731,9 +2728,6 @@
       <c r="AY57" t="s">
         <v>33</v>
       </c>
-      <c r="BB57" t="s">
-        <v>14</v>
-      </c>
       <c r="BC57" t="s">
         <v>14</v>
       </c>
@@ -2741,6 +2735,9 @@
         <v>14</v>
       </c>
       <c r="BE57" t="s">
+        <v>14</v>
+      </c>
+      <c r="BF57" t="s">
         <v>21</v>
       </c>
       <c r="BO57" t="s">
@@ -2769,10 +2766,10 @@
       <c r="AZ58" t="s">
         <v>33</v>
       </c>
-      <c r="BE58" t="s">
-        <v>14</v>
-      </c>
       <c r="BF58" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG58" t="s">
         <v>21</v>
       </c>
       <c r="BP58" t="s">
@@ -4137,6 +4134,9 @@
       <c r="CM100" t="s">
         <v>5</v>
       </c>
+      <c r="CN100" t="s">
+        <v>9</v>
+      </c>
       <c r="CO100" t="s">
         <v>34</v>
       </c>
@@ -4160,19 +4160,16 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
-      <c r="CN101" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO101" t="s">
-        <v>9</v>
-      </c>
-      <c r="CP101" t="s">
-        <v>34</v>
-      </c>
       <c r="CQ101" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="CR101" t="s">
+        <v>9</v>
+      </c>
+      <c r="CS101" t="s">
+        <v>14</v>
+      </c>
+      <c r="CT101" t="s">
         <v>21</v>
       </c>
       <c r="DG101" t="s">
@@ -4189,19 +4186,19 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="CN102" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO102" t="s">
-        <v>9</v>
-      </c>
       <c r="CQ102" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="CR102" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CS102" t="s">
+        <v>15</v>
+      </c>
+      <c r="CT102" t="s">
+        <v>14</v>
+      </c>
+      <c r="CU102" t="s">
         <v>21</v>
       </c>
       <c r="DH102" t="s">
@@ -4218,19 +4215,22 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="CN103" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO103" t="s">
-        <v>9</v>
+      <c r="CQ103" t="s">
+        <v>5</v>
       </c>
       <c r="CR103" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="CS103" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CT103" t="s">
+        <v>15</v>
+      </c>
+      <c r="CU103" t="s">
+        <v>14</v>
+      </c>
+      <c r="CV103" t="s">
         <v>21</v>
       </c>
       <c r="DI103" t="s">
@@ -4247,19 +4247,22 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
-      <c r="CN104" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO104" t="s">
-        <v>9</v>
-      </c>
-      <c r="CS104" t="s">
-        <v>34</v>
+      <c r="CQ104" t="s">
+        <v>5</v>
+      </c>
+      <c r="CR104" t="s">
+        <v>9</v>
       </c>
       <c r="CT104" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CU104" t="s">
+        <v>15</v>
+      </c>
+      <c r="CV104" t="s">
+        <v>14</v>
+      </c>
+      <c r="CW104" t="s">
         <v>21</v>
       </c>
       <c r="DJ104" t="s">
@@ -4276,19 +4279,22 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
-      <c r="CO105" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP105" t="s">
-        <v>9</v>
-      </c>
-      <c r="CT105" t="s">
-        <v>34</v>
+      <c r="CR105" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS105" t="s">
+        <v>9</v>
       </c>
       <c r="CU105" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CV105" t="s">
+        <v>15</v>
+      </c>
+      <c r="CW105" t="s">
+        <v>14</v>
+      </c>
+      <c r="CX105" t="s">
         <v>21</v>
       </c>
       <c r="DK105" t="s">
@@ -4305,19 +4311,22 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
-      <c r="CO106" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP106" t="s">
-        <v>9</v>
-      </c>
-      <c r="CU106" t="s">
-        <v>34</v>
+      <c r="CR106" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS106" t="s">
+        <v>9</v>
       </c>
       <c r="CV106" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CW106" t="s">
+        <v>15</v>
+      </c>
+      <c r="CX106" t="s">
+        <v>14</v>
+      </c>
+      <c r="CY106" t="s">
         <v>21</v>
       </c>
       <c r="DL106" t="s">
@@ -4334,19 +4343,22 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
-      <c r="CO107" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP107" t="s">
-        <v>9</v>
-      </c>
-      <c r="CV107" t="s">
-        <v>34</v>
+      <c r="CR107" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS107" t="s">
+        <v>9</v>
       </c>
       <c r="CW107" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CX107" t="s">
+        <v>15</v>
+      </c>
+      <c r="CY107" t="s">
+        <v>14</v>
+      </c>
+      <c r="CZ107" t="s">
         <v>21</v>
       </c>
       <c r="DM107" t="s">
@@ -4363,19 +4375,22 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
-      <c r="CO108" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP108" t="s">
-        <v>9</v>
-      </c>
-      <c r="CW108" t="s">
-        <v>34</v>
+      <c r="CR108" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS108" t="s">
+        <v>9</v>
       </c>
       <c r="CX108" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CY108" t="s">
+        <v>15</v>
+      </c>
+      <c r="CZ108" t="s">
+        <v>14</v>
+      </c>
+      <c r="DA108" t="s">
         <v>21</v>
       </c>
       <c r="DN108" t="s">
@@ -4392,19 +4407,22 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
-      <c r="CP109" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ109" t="s">
-        <v>9</v>
-      </c>
-      <c r="CX109" t="s">
-        <v>34</v>
+      <c r="CS109" t="s">
+        <v>5</v>
+      </c>
+      <c r="CT109" t="s">
+        <v>9</v>
       </c>
       <c r="CY109" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CZ109" t="s">
+        <v>15</v>
+      </c>
+      <c r="DA109" t="s">
+        <v>14</v>
+      </c>
+      <c r="DB109" t="s">
         <v>21</v>
       </c>
       <c r="DO109" t="s">
